--- a/LubanConfig/Moba/MiniTemplate/Datas/J-角色表.xlsx
+++ b/LubanConfig/Moba/MiniTemplate/Datas/J-角色表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="角色通用" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="200">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>ModelId</t>
   </si>
   <si>
+    <t xml:space="preserve">AttributeTemplateId </t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -73,6 +76,9 @@
     <t>模型Id</t>
   </si>
   <si>
+    <t>战斗模板Id</t>
+  </si>
+  <si>
     <t>廉颇</t>
   </si>
   <si>
@@ -451,6 +457,75 @@
     <t>PassiveSkills</t>
   </si>
   <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>MaxHp</t>
+  </si>
+  <si>
+    <t>ExtraHp</t>
+  </si>
+  <si>
+    <t>PhysicsAttack</t>
+  </si>
+  <si>
+    <t>MagicAttack</t>
+  </si>
+  <si>
+    <t>ExtraPhysicsAttack</t>
+  </si>
+  <si>
+    <t>ExtraMagicAttack</t>
+  </si>
+  <si>
+    <t>PhysicsDefense</t>
+  </si>
+  <si>
+    <t>MagicDefense</t>
+  </si>
+  <si>
+    <t>Mana</t>
+  </si>
+  <si>
+    <t>MaxMana</t>
+  </si>
+  <si>
+    <t>CriticalR</t>
+  </si>
+  <si>
+    <t>AttackSpeedR</t>
+  </si>
+  <si>
+    <t>CooldownReduceR</t>
+  </si>
+  <si>
+    <t>PhysicsPenetrationR</t>
+  </si>
+  <si>
+    <t>MagicPenetrationR</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>PhysicsBloodsuckingR</t>
+  </si>
+  <si>
+    <t>MagicBloodsuckingR</t>
+  </si>
+  <si>
+    <t>AttackRange</t>
+  </si>
+  <si>
+    <t>PerSecondBloodR</t>
+  </si>
+  <si>
+    <t>PerSecondManaR</t>
+  </si>
+  <si>
+    <t>ResilienceR</t>
+  </si>
+  <si>
     <t>升级战斗属性方案</t>
   </si>
   <si>
@@ -460,6 +535,75 @@
     <t>被动技能</t>
   </si>
   <si>
+    <t>属性1</t>
+  </si>
+  <si>
+    <t>属性2</t>
+  </si>
+  <si>
+    <t>属性3</t>
+  </si>
+  <si>
+    <t>属性4</t>
+  </si>
+  <si>
+    <t>属性5</t>
+  </si>
+  <si>
+    <t>属性6</t>
+  </si>
+  <si>
+    <t>属性7</t>
+  </si>
+  <si>
+    <t>属性8</t>
+  </si>
+  <si>
+    <t>属性9</t>
+  </si>
+  <si>
+    <t>属性10</t>
+  </si>
+  <si>
+    <t>属性11</t>
+  </si>
+  <si>
+    <t>属性12</t>
+  </si>
+  <si>
+    <t>属性13</t>
+  </si>
+  <si>
+    <t>属性14</t>
+  </si>
+  <si>
+    <t>属性15</t>
+  </si>
+  <si>
+    <t>属性16</t>
+  </si>
+  <si>
+    <t>属性17</t>
+  </si>
+  <si>
+    <t>属性18</t>
+  </si>
+  <si>
+    <t>属性19</t>
+  </si>
+  <si>
+    <t>属性20</t>
+  </si>
+  <si>
+    <t>属性21</t>
+  </si>
+  <si>
+    <t>属性22</t>
+  </si>
+  <si>
+    <t>属性23</t>
+  </si>
+  <si>
     <t>10010101,10010201,10010301</t>
   </si>
   <si>
@@ -467,9 +611,6 @@
   </si>
   <si>
     <t>Level</t>
-  </si>
-  <si>
-    <t>MaxHp</t>
   </si>
   <si>
     <t>Attack</t>
@@ -1491,40 +1632,49 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="K1" s="4"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:9">
@@ -1532,12 +1682,14 @@
         <v>1001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2">
         <v>1001</v>
       </c>
-      <c r="F4" s="2"/>
+      <c r="F4" s="2">
+        <v>1001</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1547,46 +1699,57 @@
         <v>1002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2">
         <v>1002</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2">
+        <v>1002</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:6">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2">
         <v>1003</v>
       </c>
-    </row>
-    <row r="7" spans="2:5">
+      <c r="F6" s="2">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2">
         <v>1004</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
+      <c r="F7" s="2">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2">
+        <v>1005</v>
+      </c>
+      <c r="F8" s="2">
         <v>1005</v>
       </c>
     </row>
@@ -1595,9 +1758,12 @@
         <v>1006</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2">
+        <v>1006</v>
+      </c>
+      <c r="F9" s="2">
         <v>1006</v>
       </c>
       <c r="J9" s="2"/>
@@ -1607,1286 +1773,1637 @@
         <v>1007</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" s="2">
         <v>1007</v>
       </c>
+      <c r="F10" s="2">
+        <v>1007</v>
+      </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="2:6">
       <c r="B11" s="2">
         <v>1008</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2">
         <v>1008</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
+      <c r="F11" s="2">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
       <c r="B12" s="2">
         <v>1009</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2">
         <v>1009</v>
       </c>
-    </row>
-    <row r="13" spans="2:5">
+      <c r="F12" s="2">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
       <c r="B13" s="2">
         <v>1010</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2">
         <v>1010</v>
       </c>
-    </row>
-    <row r="14" spans="2:5">
+      <c r="F13" s="2">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
       <c r="B14" s="2">
         <v>1011</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2">
         <v>1011</v>
       </c>
-    </row>
-    <row r="15" spans="2:5">
+      <c r="F14" s="2">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
       <c r="B15" s="2">
         <v>1012</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2">
         <v>1012</v>
       </c>
-    </row>
-    <row r="16" spans="2:5">
+      <c r="F15" s="2">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
       <c r="B16" s="2">
         <v>1013</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E16" s="2">
         <v>1013</v>
       </c>
-    </row>
-    <row r="17" spans="2:5">
+      <c r="F16" s="2">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
       <c r="B17" s="2">
         <v>1014</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2">
         <v>1014</v>
       </c>
-    </row>
-    <row r="18" spans="2:5">
+      <c r="F17" s="2">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="2">
         <v>1015</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2">
         <v>1015</v>
       </c>
-    </row>
-    <row r="19" spans="2:5">
+      <c r="F18" s="2">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" s="2">
         <v>1016</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>1016</v>
       </c>
-    </row>
-    <row r="20" spans="2:5">
+      <c r="F19" s="2">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="2">
         <v>1017</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2">
         <v>1017</v>
       </c>
-    </row>
-    <row r="21" spans="2:5">
+      <c r="F20" s="2">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
       <c r="B21" s="2">
         <v>1018</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2">
         <v>1018</v>
       </c>
-    </row>
-    <row r="22" spans="2:5">
+      <c r="F21" s="2">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
       <c r="B22" s="2">
         <v>1019</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2">
         <v>1019</v>
       </c>
-    </row>
-    <row r="23" spans="2:5">
+      <c r="F22" s="2">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
       <c r="B23" s="2">
         <v>1020</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <v>1020</v>
       </c>
-    </row>
-    <row r="24" spans="2:5">
+      <c r="F23" s="2">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
       <c r="B24" s="2">
         <v>1021</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2">
         <v>1021</v>
       </c>
-    </row>
-    <row r="25" spans="2:5">
+      <c r="F24" s="2">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
       <c r="B25" s="2">
         <v>1022</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2">
         <v>1022</v>
       </c>
-    </row>
-    <row r="26" spans="2:5">
+      <c r="F25" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
       <c r="B26" s="2">
         <v>1023</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2">
         <v>1023</v>
       </c>
-    </row>
-    <row r="27" spans="2:5">
+      <c r="F26" s="2">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="B27" s="2">
         <v>1024</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2">
         <v>1024</v>
       </c>
-    </row>
-    <row r="28" spans="2:5">
+      <c r="F27" s="2">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
       <c r="B28" s="2">
         <v>1025</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2">
         <v>1025</v>
       </c>
-    </row>
-    <row r="29" spans="2:5">
+      <c r="F28" s="2">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
       <c r="B29" s="2">
         <v>1026</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2">
         <v>1026</v>
       </c>
-    </row>
-    <row r="30" ht="12.95" customHeight="1" spans="2:5">
+      <c r="F29" s="2">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="30" ht="12.95" customHeight="1" spans="2:6">
       <c r="B30" s="2">
         <v>1027</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E30" s="2">
         <v>1027</v>
       </c>
-    </row>
-    <row r="31" spans="2:5">
+      <c r="F30" s="2">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="2">
         <v>1028</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E31" s="2">
         <v>1028</v>
       </c>
-    </row>
-    <row r="32" spans="2:5">
+      <c r="F31" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="2">
         <v>1029</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2">
         <v>1029</v>
       </c>
-    </row>
-    <row r="33" spans="2:5">
+      <c r="F32" s="2">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
       <c r="B33" s="2">
         <v>1030</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2">
         <v>1030</v>
       </c>
-    </row>
-    <row r="34" spans="2:5">
+      <c r="F33" s="2">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="2">
         <v>1031</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E34" s="2">
         <v>1031</v>
       </c>
-    </row>
-    <row r="35" spans="2:5">
+      <c r="F34" s="2">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
       <c r="B35" s="2">
         <v>1032</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E35" s="2">
         <v>1032</v>
       </c>
-    </row>
-    <row r="36" spans="2:5">
+      <c r="F35" s="2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
       <c r="B36" s="2">
         <v>1033</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E36" s="2">
         <v>1033</v>
       </c>
-    </row>
-    <row r="37" spans="2:5">
+      <c r="F36" s="2">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="2">
         <v>1034</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E37" s="2">
         <v>1034</v>
       </c>
-    </row>
-    <row r="38" spans="2:5">
+      <c r="F37" s="2">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
       <c r="B38" s="2">
         <v>1035</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2">
         <v>1035</v>
       </c>
-    </row>
-    <row r="39" spans="2:5">
+      <c r="F38" s="2">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="2">
         <v>1036</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2">
         <v>1036</v>
       </c>
-    </row>
-    <row r="40" spans="2:5">
+      <c r="F39" s="2">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="2">
         <v>1037</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2">
         <v>1037</v>
       </c>
-    </row>
-    <row r="41" spans="2:5">
+      <c r="F40" s="2">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="2">
         <v>1038</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2">
         <v>1038</v>
       </c>
-    </row>
-    <row r="42" spans="2:5">
+      <c r="F41" s="2">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
       <c r="B42" s="2">
         <v>1039</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2">
         <v>1039</v>
       </c>
-    </row>
-    <row r="43" spans="2:5">
+      <c r="F42" s="2">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
       <c r="B43" s="2">
         <v>1040</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E43" s="2">
         <v>1040</v>
       </c>
-    </row>
-    <row r="44" spans="2:5">
+      <c r="F43" s="2">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="2">
         <v>1041</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E44" s="2">
         <v>1041</v>
       </c>
-    </row>
-    <row r="45" spans="2:5">
+      <c r="F44" s="2">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="2">
         <v>1042</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E45" s="2">
         <v>1042</v>
       </c>
-    </row>
-    <row r="46" spans="2:5">
+      <c r="F45" s="2">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="2">
         <v>1043</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E46" s="2">
         <v>1043</v>
       </c>
-    </row>
-    <row r="47" spans="2:5">
+      <c r="F46" s="2">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
       <c r="B47" s="2">
         <v>1044</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E47" s="2">
         <v>1044</v>
       </c>
-    </row>
-    <row r="48" spans="2:5">
+      <c r="F47" s="2">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="2">
         <v>1045</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2">
         <v>1045</v>
       </c>
-    </row>
-    <row r="49" spans="2:5">
+      <c r="F48" s="2">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
       <c r="B49" s="2">
         <v>1046</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E49" s="2">
         <v>1046</v>
       </c>
-    </row>
-    <row r="50" spans="2:5">
+      <c r="F49" s="2">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
       <c r="B50" s="2">
         <v>1047</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E50" s="2">
         <v>1047</v>
       </c>
-    </row>
-    <row r="51" spans="2:5">
+      <c r="F50" s="2">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="2">
         <v>1048</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2">
         <v>1048</v>
       </c>
-    </row>
-    <row r="52" spans="2:5">
+      <c r="F51" s="2">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="2">
         <v>1049</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E52" s="2">
         <v>1049</v>
       </c>
-    </row>
-    <row r="53" spans="2:5">
+      <c r="F52" s="2">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
       <c r="B53" s="2">
         <v>1050</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E53" s="2">
         <v>1050</v>
       </c>
-    </row>
-    <row r="54" spans="2:5">
+      <c r="F53" s="2">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
       <c r="B54" s="2">
         <v>1051</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E54" s="2">
         <v>1051</v>
       </c>
-    </row>
-    <row r="55" spans="2:5">
+      <c r="F54" s="2">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="2">
         <v>1052</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E55" s="2">
         <v>1052</v>
       </c>
-    </row>
-    <row r="56" spans="2:5">
+      <c r="F55" s="2">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
       <c r="B56" s="2">
         <v>1053</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E56" s="2">
         <v>1053</v>
       </c>
-    </row>
-    <row r="57" spans="2:5">
+      <c r="F56" s="2">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
       <c r="B57" s="2">
         <v>1054</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E57" s="2">
         <v>1054</v>
       </c>
-    </row>
-    <row r="58" spans="2:5">
+      <c r="F57" s="2">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
       <c r="B58" s="2">
         <v>1055</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E58" s="2">
         <v>1055</v>
       </c>
-    </row>
-    <row r="59" spans="2:5">
+      <c r="F58" s="2">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="2">
         <v>1056</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E59" s="2">
         <v>1056</v>
       </c>
-    </row>
-    <row r="60" spans="2:5">
+      <c r="F59" s="2">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="2">
         <v>1057</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E60" s="2">
         <v>1057</v>
       </c>
-    </row>
-    <row r="61" spans="2:5">
+      <c r="F60" s="2">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
       <c r="B61" s="2">
         <v>1058</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E61" s="2">
         <v>1058</v>
       </c>
-    </row>
-    <row r="62" spans="2:5">
+      <c r="F61" s="2">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
       <c r="B62" s="2">
         <v>1059</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E62" s="2">
         <v>1059</v>
       </c>
-    </row>
-    <row r="63" spans="2:5">
+      <c r="F62" s="2">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
       <c r="B63" s="2">
         <v>1060</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E63" s="2">
         <v>1060</v>
       </c>
-    </row>
-    <row r="64" spans="2:5">
+      <c r="F63" s="2">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="2">
         <v>1061</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E64" s="2">
         <v>1061</v>
       </c>
-    </row>
-    <row r="65" spans="2:5">
+      <c r="F64" s="2">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="2">
         <v>1062</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2">
         <v>1062</v>
       </c>
-    </row>
-    <row r="66" spans="2:5">
+      <c r="F65" s="2">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="2">
         <v>1063</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2">
         <v>1063</v>
       </c>
-    </row>
-    <row r="67" spans="2:5">
+      <c r="F66" s="2">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
       <c r="B67" s="2">
         <v>1064</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2">
         <v>1064</v>
       </c>
-    </row>
-    <row r="68" spans="2:5">
+      <c r="F67" s="2">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
       <c r="B68" s="2">
         <v>1065</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E68" s="2">
         <v>1065</v>
       </c>
-    </row>
-    <row r="69" spans="2:5">
+      <c r="F68" s="2">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
       <c r="B69" s="2">
         <v>1066</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2">
         <v>1066</v>
       </c>
-    </row>
-    <row r="70" spans="2:5">
+      <c r="F69" s="2">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6">
       <c r="B70" s="2">
         <v>1067</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2">
         <v>1067</v>
       </c>
-    </row>
-    <row r="71" spans="2:5">
+      <c r="F70" s="2">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="2">
         <v>1068</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E71" s="2">
         <v>1068</v>
       </c>
-    </row>
-    <row r="72" spans="2:5">
+      <c r="F71" s="2">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
       <c r="B72" s="2">
         <v>1069</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E72" s="2">
         <v>1069</v>
       </c>
-    </row>
-    <row r="73" spans="2:5">
+      <c r="F72" s="2">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6">
       <c r="B73" s="2">
         <v>1070</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E73" s="2">
         <v>1070</v>
       </c>
-    </row>
-    <row r="74" spans="2:5">
+      <c r="F73" s="2">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6">
       <c r="B74" s="2">
         <v>1071</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E74" s="2">
         <v>1071</v>
       </c>
-    </row>
-    <row r="75" spans="2:5">
+      <c r="F74" s="2">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
       <c r="B75" s="2">
         <v>1072</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E75" s="2">
         <v>1072</v>
       </c>
-    </row>
-    <row r="76" spans="2:5">
+      <c r="F75" s="2">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="2">
         <v>1073</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E76" s="2">
         <v>1073</v>
       </c>
-    </row>
-    <row r="77" spans="2:5">
+      <c r="F76" s="2">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6">
       <c r="B77" s="2">
         <v>1074</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2">
         <v>1074</v>
       </c>
-    </row>
-    <row r="78" spans="2:5">
+      <c r="F77" s="2">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6">
       <c r="B78" s="2">
         <v>1075</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E78" s="2">
         <v>1075</v>
       </c>
-    </row>
-    <row r="79" spans="2:5">
+      <c r="F78" s="2">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6">
       <c r="B79" s="2">
         <v>1076</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E79" s="2">
         <v>1076</v>
       </c>
-    </row>
-    <row r="80" spans="2:5">
+      <c r="F79" s="2">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="2">
         <v>1077</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E80" s="2">
         <v>1077</v>
       </c>
-    </row>
-    <row r="81" spans="2:5">
+      <c r="F80" s="2">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6">
       <c r="B81" s="2">
         <v>1078</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E81" s="2">
         <v>1078</v>
       </c>
-    </row>
-    <row r="82" spans="2:5">
+      <c r="F81" s="2">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="2">
         <v>1079</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E82" s="2">
         <v>1079</v>
       </c>
-    </row>
-    <row r="83" spans="2:5">
+      <c r="F82" s="2">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6">
       <c r="B83" s="2">
         <v>1080</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E83" s="2">
         <v>1080</v>
       </c>
-    </row>
-    <row r="84" spans="2:5">
+      <c r="F83" s="2">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="2">
         <v>1081</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E84" s="2">
         <v>1081</v>
       </c>
-    </row>
-    <row r="85" spans="2:5">
+      <c r="F84" s="2">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6">
       <c r="B85" s="2">
         <v>1082</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E85" s="2">
         <v>1082</v>
       </c>
-    </row>
-    <row r="86" spans="2:5">
+      <c r="F85" s="2">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="2">
         <v>1083</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E86" s="2">
         <v>1083</v>
       </c>
-    </row>
-    <row r="87" spans="2:5">
+      <c r="F86" s="2">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6">
       <c r="B87" s="2">
         <v>1084</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E87" s="2">
         <v>1084</v>
       </c>
-    </row>
-    <row r="88" spans="2:5">
+      <c r="F87" s="2">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6">
       <c r="B88" s="2">
         <v>1085</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E88" s="2">
         <v>1085</v>
       </c>
-    </row>
-    <row r="89" spans="2:5">
+      <c r="F88" s="2">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6">
       <c r="B89" s="2">
         <v>1086</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E89" s="2">
         <v>1086</v>
       </c>
-    </row>
-    <row r="90" spans="2:5">
+      <c r="F89" s="2">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6">
       <c r="B90" s="2">
         <v>1087</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E90" s="2">
         <v>1087</v>
       </c>
-    </row>
-    <row r="91" spans="2:5">
+      <c r="F90" s="2">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6">
       <c r="B91" s="2">
         <v>1088</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E91" s="2">
         <v>1088</v>
       </c>
-    </row>
-    <row r="92" spans="2:5">
+      <c r="F91" s="2">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6">
       <c r="B92" s="2">
         <v>1089</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E92" s="2">
         <v>1089</v>
       </c>
-    </row>
-    <row r="93" spans="2:5">
+      <c r="F92" s="2">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="2">
         <v>1090</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E93" s="2">
         <v>1090</v>
       </c>
-    </row>
-    <row r="94" spans="2:5">
+      <c r="F93" s="2">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6">
       <c r="B94" s="2">
         <v>1091</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E94" s="2">
         <v>1091</v>
       </c>
-    </row>
-    <row r="95" spans="2:5">
+      <c r="F94" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6">
       <c r="B95" s="2">
         <v>1092</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E95" s="2">
         <v>1092</v>
       </c>
-    </row>
-    <row r="96" spans="2:5">
+      <c r="F95" s="2">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6">
       <c r="B96" s="2">
         <v>1093</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E96" s="2">
         <v>1093</v>
       </c>
-    </row>
-    <row r="97" spans="2:5">
+      <c r="F96" s="2">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6">
       <c r="B97" s="2">
         <v>1094</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E97" s="2">
         <v>1094</v>
       </c>
-    </row>
-    <row r="98" spans="2:5">
+      <c r="F97" s="2">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="2">
         <v>1095</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E98" s="2">
         <v>1095</v>
       </c>
-    </row>
-    <row r="99" spans="2:5">
+      <c r="F98" s="2">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6">
       <c r="B99" s="2">
         <v>1096</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E99" s="2">
         <v>1096</v>
       </c>
-    </row>
-    <row r="100" spans="2:5">
+      <c r="F99" s="2">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="2">
         <v>1097</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E100" s="2">
         <v>1097</v>
       </c>
-    </row>
-    <row r="101" spans="2:5">
+      <c r="F100" s="2">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
       <c r="B101" s="2">
         <v>1098</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E101" s="2">
         <v>1098</v>
       </c>
-    </row>
-    <row r="102" spans="2:5">
+      <c r="F101" s="2">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="2">
         <v>1099</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E102" s="2">
         <v>1099</v>
       </c>
-    </row>
-    <row r="103" spans="2:5">
+      <c r="F102" s="2">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
       <c r="B103" s="2">
         <v>1100</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E103" s="2">
         <v>1100</v>
       </c>
-    </row>
-    <row r="104" spans="2:5">
+      <c r="F103" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
       <c r="B104" s="2">
         <v>1101</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E104" s="2">
         <v>1101</v>
       </c>
-    </row>
-    <row r="105" spans="2:5">
+      <c r="F104" s="2">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
       <c r="B105" s="2">
         <v>1102</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E105" s="2">
         <v>1102</v>
       </c>
-    </row>
-    <row r="106" spans="2:5">
+      <c r="F105" s="2">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6">
       <c r="B106" s="2">
         <v>1103</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E106" s="2">
         <v>1103</v>
       </c>
-    </row>
-    <row r="107" spans="2:5">
+      <c r="F106" s="2">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
       <c r="B107" s="2">
         <v>1104</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E107" s="2">
         <v>1104</v>
       </c>
-    </row>
-    <row r="108" spans="2:5">
+      <c r="F107" s="2">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="2">
         <v>1105</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E108" s="2">
         <v>1105</v>
       </c>
-    </row>
-    <row r="109" spans="2:5">
+      <c r="F108" s="2">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
       <c r="B109" s="2">
         <v>1106</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E109" s="2">
         <v>1106</v>
       </c>
-    </row>
-    <row r="110" spans="2:5">
+      <c r="F109" s="2">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="2">
         <v>1107</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E110" s="2">
         <v>1107</v>
       </c>
-    </row>
-    <row r="111" spans="2:5">
+      <c r="F110" s="2">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6">
       <c r="B111" s="2">
         <v>1108</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E111" s="2">
         <v>1108</v>
       </c>
-    </row>
-    <row r="112" spans="2:5">
+      <c r="F111" s="2">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
       <c r="B112" s="2">
         <v>1109</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E112" s="2">
         <v>1109</v>
       </c>
-    </row>
-    <row r="113" spans="2:5">
+      <c r="F112" s="2">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6">
       <c r="B113" s="2">
         <v>1110</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E113" s="2">
         <v>1110</v>
       </c>
-    </row>
-    <row r="114" spans="2:5">
+      <c r="F113" s="2">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6">
       <c r="B114" s="2">
         <v>1111</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E114" s="2">
         <v>1111</v>
       </c>
-    </row>
-    <row r="115" spans="2:5">
+      <c r="F114" s="2">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6">
       <c r="B115" s="2">
         <v>1112</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E115" s="2">
         <v>1112</v>
       </c>
-    </row>
-    <row r="116" spans="2:5">
+      <c r="F115" s="2">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="2">
         <v>1113</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E116" s="2">
         <v>1113</v>
       </c>
-    </row>
-    <row r="117" spans="2:5">
+      <c r="F116" s="2">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6">
       <c r="B117" s="2">
         <v>1114</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E117" s="2">
         <v>1114</v>
       </c>
-    </row>
-    <row r="118" spans="2:5">
+      <c r="F117" s="2">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6">
       <c r="B118" s="2">
         <v>1115</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E118" s="2">
         <v>1115</v>
       </c>
-    </row>
-    <row r="119" spans="2:5">
+      <c r="F118" s="2">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="2">
         <v>1116</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E119" s="2">
         <v>1116</v>
       </c>
-    </row>
-    <row r="120" spans="2:5">
+      <c r="F119" s="2">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="2">
         <v>1117</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E120" s="2">
         <v>1117</v>
       </c>
-    </row>
-    <row r="121" spans="2:5">
+      <c r="F120" s="2">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="2">
         <v>1118</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E121" s="2">
         <v>1118</v>
       </c>
-    </row>
-    <row r="122" spans="2:5">
+      <c r="F121" s="2">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="2">
         <v>1119</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E122" s="2">
         <v>1119</v>
       </c>
-    </row>
-    <row r="123" spans="2:5">
+      <c r="F122" s="2">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6">
       <c r="B123" s="2">
         <v>1120</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E123" s="2">
         <v>1120</v>
       </c>
-    </row>
-    <row r="124" spans="2:5">
+      <c r="F123" s="2">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
       <c r="B124" s="2">
         <v>1121</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E124" s="2">
         <v>1121</v>
       </c>
-    </row>
-    <row r="125" spans="2:5">
+      <c r="F124" s="2">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="2">
         <v>1122</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E125" s="2">
         <v>1122</v>
       </c>
-    </row>
-    <row r="126" spans="2:5">
+      <c r="F125" s="2">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6">
       <c r="B126" s="2">
         <v>1123</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E126" s="2">
+        <v>1123</v>
+      </c>
+      <c r="F126" s="2">
         <v>1123</v>
       </c>
     </row>
@@ -2900,14 +3417,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="5" width="22.25" customWidth="1"/>
     <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="10" max="10" width="16.875" customWidth="1"/>
+    <col min="11" max="11" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:43">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2918,37 +3438,83 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
@@ -2962,49 +3528,96 @@
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
-    </row>
-    <row r="2" spans="1:42">
+      <c r="AQ1" s="1"/>
+    </row>
+    <row r="2" spans="1:43">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
@@ -3018,49 +3631,96 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
       <c r="AP2" s="1"/>
-    </row>
-    <row r="3" spans="1:42">
+      <c r="AQ2" s="1"/>
+    </row>
+    <row r="3" spans="1:43">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
+        <v>167</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -3074,8 +3734,9 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="1"/>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="AQ3" s="1"/>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="1"/>
       <c r="B4" s="2">
         <v>1001</v>
@@ -3085,10 +3746,28 @@
         <v>10001</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>191</v>
+      </c>
+      <c r="G4" s="1">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>200</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="W4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" s="1"/>
       <c r="B5" s="2">
         <v>1002</v>
@@ -3098,7 +3777,25 @@
         <v>10002</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>144</v>
+        <v>192</v>
+      </c>
+      <c r="G5" s="1">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>200</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="W5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3121,13 +3818,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3159,19 +3856,19 @@
     </row>
     <row r="2" spans="1:120">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -3291,19 +3988,19 @@
     </row>
     <row r="3" spans="1:120">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
